--- a/Result/profitability/5489.xlsx
+++ b/Result/profitability/5489.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5487500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>36.61</v>
+        <v>35.5625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0.58375</v>
+        <v>0.5287500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>36.74125</v>
+        <v>35.695</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>0.54375</v>
+        <v>0.54125</v>
       </c>
       <c r="N4" t="n">
-        <v>37.2475</v>
+        <v>36.325</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.19</v>
       </c>
       <c r="M5" t="n">
-        <v>0.50875</v>
+        <v>0.55125</v>
       </c>
       <c r="N5" t="n">
-        <v>37.745</v>
+        <v>36.87375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5525</v>
+        <v>0.5125</v>
       </c>
       <c r="N6" t="n">
-        <v>37.9675</v>
+        <v>37.495</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0.535</v>
+        <v>0.5087499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>39.3325</v>
+        <v>38.86</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>40.565</v>
+        <v>40.44375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.58625</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>42.29125000000001</v>
@@ -9344,15 +9344,15 @@
         <v>37.03</v>
       </c>
       <c r="G71" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>22.03%</t>
+          <t>16.06%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-86</v>
+        <v>-59</v>
       </c>
       <c r="J71" t="n">
         <v>13</v>
@@ -9471,7 +9471,7 @@
         <v>33.84</v>
       </c>
       <c r="G72" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="J72" t="n">
         <v>91</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5489</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>514</v>
+      </c>
+      <c r="D75" t="n">
+        <v>360</v>
+      </c>
+      <c r="E75" t="n">
+        <v>155</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.90%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>53</v>
+      </c>
+      <c r="K75" t="n">
+        <v>44</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.01375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5517241379310347</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9700000000000024</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03126007089912997</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.090909090909091</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.970000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1882257628949501</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
